--- a/db/generator/exports/sample_upload_3.xlsx
+++ b/db/generator/exports/sample_upload_3.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,675 +446,783 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46878</t>
+          <t>153152</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12025</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>151.26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>841.43</t>
+          <t>108.32</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>41011</t>
+          <t>269529</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>702.95</t>
+          <t>297.23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>809.41</t>
+          <t>201.91</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>48422</t>
+          <t>499518</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>702.95</t>
+          <t>483.62</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>681.6</t>
+          <t>321.35</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45011</t>
+          <t>501809</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12050</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>702.97</t>
+          <t>462.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>738.58</t>
+          <t>301.05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>46013</t>
+          <t>452721</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>702.96</t>
+          <t>452.81</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>629.59</t>
+          <t>272.88</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46630</t>
+          <t>492835</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11106</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>702.97</t>
+          <t>436.37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>548.05</t>
+          <t>223.63</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>46679</t>
+          <t>482399</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11466</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>702.98</t>
+          <t>439.08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>600.41</t>
+          <t>227.42</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>53994</t>
+          <t>500663</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12759</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>702.95</t>
+          <t>466.56</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>788.41</t>
+          <t>337.94</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>45855</t>
+          <t>430166</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>702.97</t>
+          <t>469.78</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>834.92</t>
+          <t>350.51</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>49534</t>
+          <t>436088</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11934</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>410.89</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>733.8</t>
+          <t>234.93</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>44122</t>
+          <t>445595</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>702.98</t>
+          <t>451.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>713.42</t>
+          <t>308.59</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>43907</t>
+          <t>532303</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>702.95</t>
+          <t>484.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>623.02</t>
+          <t>293.63</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>48269</t>
+          <t>465093</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>702.95</t>
+          <t>453.19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>540.19</t>
+          <t>242.79</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>45699</t>
+          <t>512765</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11945</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>702.96</t>
+          <t>472.79</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>629.03</t>
+          <t>222.72</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>48075</t>
+          <t>434485</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>702.98</t>
+          <t>446.04</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>732.18</t>
+          <t>271.09</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>44269</t>
+          <t>477090</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>702.95</t>
+          <t>456.55</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>721.11</t>
+          <t>302.18</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>51625</t>
+          <t>448517</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>12866</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>702.97</t>
+          <t>467.22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>722.65</t>
+          <t>249.63</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>49622</t>
+          <t>495669</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>702.96</t>
+          <t>472.43</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>715.58</t>
+          <t>258.52</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>48157</t>
+          <t>491984</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>11644</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>702.98</t>
+          <t>471.84</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>534.06</t>
+          <t>332.66</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>49810</t>
+          <t>455122</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>465.95</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>520.49</t>
+          <t>238.68</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>47546</t>
+          <t>543798</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>11884</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>702.97</t>
+          <t>489.32</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>538.98</t>
+          <t>226.19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>47830</t>
+          <t>481612</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11804</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>702.98</t>
+          <t>453.26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>678.01</t>
+          <t>268.31</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>46122</t>
+          <t>472517</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11879</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>702.99</t>
+          <t>460.99</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>762.75</t>
+          <t>245.77</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>47234</t>
+          <t>527584</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>702.96</t>
+          <t>481.07</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>624.07</t>
+          <t>290.37</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>48023</t>
+          <t>462698</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>12140</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>433.62</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>693.08</t>
+          <t>272.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>440910</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3557</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>445.77</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>229.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>474959</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3811</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>423.86</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>215.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>439873</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3907</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>460.44</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>292.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>506082</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3977</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>470.09</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>343.02</t>
         </is>
       </c>
     </row>
